--- a/Datas/ProfessionDataList.xlsx
+++ b/Datas/ProfessionDataList.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="343">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1141,6 +1141,10 @@
   </si>
   <si>
     <t>professionEditorDatas</t>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1519,14 +1523,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
     <col min="2" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>340</v>
       </c>
@@ -1534,7 +1538,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>323</v>
       </c>
@@ -1574,8 +1578,11 @@
       <c r="M2" s="1" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.15">
+      <c r="N2" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>325</v>
       </c>
@@ -1613,10 +1620,13 @@
         <v>338</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1654,10 +1664,13 @@
         <v>100</v>
       </c>
       <c r="M4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+        <v>100</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1695,10 +1708,13 @@
         <v>100</v>
       </c>
       <c r="M5" s="1">
+        <v>100</v>
+      </c>
+      <c r="N5" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1736,10 +1752,13 @@
         <v>100</v>
       </c>
       <c r="M6" s="1">
+        <v>100</v>
+      </c>
+      <c r="N6" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -1777,10 +1796,13 @@
         <v>100</v>
       </c>
       <c r="M7" s="1">
+        <v>100</v>
+      </c>
+      <c r="N7" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -1818,10 +1840,13 @@
         <v>100</v>
       </c>
       <c r="M8" s="1">
+        <v>100</v>
+      </c>
+      <c r="N8" s="1">
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -1859,10 +1884,13 @@
         <v>100</v>
       </c>
       <c r="M9" s="1">
+        <v>100</v>
+      </c>
+      <c r="N9" s="1">
         <v>186</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -1900,10 +1928,13 @@
         <v>100</v>
       </c>
       <c r="M10" s="1">
+        <v>100</v>
+      </c>
+      <c r="N10" s="1">
         <v>311</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1941,10 +1972,13 @@
         <v>100</v>
       </c>
       <c r="M11" s="1">
+        <v>100</v>
+      </c>
+      <c r="N11" s="1">
         <v>503</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1982,10 +2016,13 @@
         <v>100</v>
       </c>
       <c r="M12" s="1">
+        <v>100</v>
+      </c>
+      <c r="N12" s="1">
         <v>786</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -2023,10 +2060,13 @@
         <v>100</v>
       </c>
       <c r="M13" s="1">
+        <v>100</v>
+      </c>
+      <c r="N13" s="1">
         <v>1187</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -2064,10 +2104,13 @@
         <v>100</v>
       </c>
       <c r="M14" s="1">
+        <v>100</v>
+      </c>
+      <c r="N14" s="1">
         <v>1738</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -2105,10 +2148,13 @@
         <v>100</v>
       </c>
       <c r="M15" s="1">
+        <v>100</v>
+      </c>
+      <c r="N15" s="1">
         <v>2472</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -2146,10 +2192,13 @@
         <v>100</v>
       </c>
       <c r="M16" s="1">
+        <v>100</v>
+      </c>
+      <c r="N16" s="1">
         <v>3428</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -2187,10 +2236,13 @@
         <v>100</v>
       </c>
       <c r="M17" s="1">
+        <v>100</v>
+      </c>
+      <c r="N17" s="1">
         <v>4649</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -2228,10 +2280,13 @@
         <v>100</v>
       </c>
       <c r="M18" s="1">
+        <v>100</v>
+      </c>
+      <c r="N18" s="1">
         <v>6178</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -2269,10 +2324,13 @@
         <v>100</v>
       </c>
       <c r="M19" s="1">
+        <v>100</v>
+      </c>
+      <c r="N19" s="1">
         <v>8067</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -2310,10 +2368,13 @@
         <v>100</v>
       </c>
       <c r="M20" s="1">
+        <v>100</v>
+      </c>
+      <c r="N20" s="1">
         <v>10366</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -2351,10 +2412,13 @@
         <v>100</v>
       </c>
       <c r="M21" s="1">
+        <v>100</v>
+      </c>
+      <c r="N21" s="1">
         <v>13134</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>1</v>
       </c>
@@ -2392,10 +2456,13 @@
         <v>100</v>
       </c>
       <c r="M22" s="1">
+        <v>100</v>
+      </c>
+      <c r="N22" s="1">
         <v>16429</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>1</v>
       </c>
@@ -2433,10 +2500,13 @@
         <v>100</v>
       </c>
       <c r="M23" s="1">
+        <v>100</v>
+      </c>
+      <c r="N23" s="1">
         <v>20315</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -2474,10 +2544,13 @@
         <v>100</v>
       </c>
       <c r="M24" s="1">
+        <v>100</v>
+      </c>
+      <c r="N24" s="1">
         <v>24861</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>1</v>
       </c>
@@ -2515,10 +2588,13 @@
         <v>100</v>
       </c>
       <c r="M25" s="1">
+        <v>100</v>
+      </c>
+      <c r="N25" s="1">
         <v>30136</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -2556,10 +2632,13 @@
         <v>100</v>
       </c>
       <c r="M26" s="1">
+        <v>100</v>
+      </c>
+      <c r="N26" s="1">
         <v>36216</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>1</v>
       </c>
@@ -2597,10 +2676,13 @@
         <v>100</v>
       </c>
       <c r="M27" s="1">
+        <v>100</v>
+      </c>
+      <c r="N27" s="1">
         <v>43178</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>1</v>
       </c>
@@ -2638,10 +2720,13 @@
         <v>100</v>
       </c>
       <c r="M28" s="1">
+        <v>100</v>
+      </c>
+      <c r="N28" s="1">
         <v>51105</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -2679,10 +2764,13 @@
         <v>100</v>
       </c>
       <c r="M29" s="1">
+        <v>100</v>
+      </c>
+      <c r="N29" s="1">
         <v>60082</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>1</v>
       </c>
@@ -2720,10 +2808,13 @@
         <v>100</v>
       </c>
       <c r="M30" s="1">
+        <v>100</v>
+      </c>
+      <c r="N30" s="1">
         <v>70199</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>1</v>
       </c>
@@ -2761,10 +2852,13 @@
         <v>100</v>
       </c>
       <c r="M31" s="1">
+        <v>100</v>
+      </c>
+      <c r="N31" s="1">
         <v>81547</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -2802,10 +2896,13 @@
         <v>100</v>
       </c>
       <c r="M32" s="1">
+        <v>100</v>
+      </c>
+      <c r="N32" s="1">
         <v>94225</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>1</v>
       </c>
@@ -2843,10 +2940,13 @@
         <v>100</v>
       </c>
       <c r="M33" s="1">
+        <v>100</v>
+      </c>
+      <c r="N33" s="1">
         <v>108330</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>1</v>
       </c>
@@ -2884,10 +2984,13 @@
         <v>100</v>
       </c>
       <c r="M34" s="1">
+        <v>100</v>
+      </c>
+      <c r="N34" s="1">
         <v>123968</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>1</v>
       </c>
@@ -2925,10 +3028,13 @@
         <v>100</v>
       </c>
       <c r="M35" s="1">
+        <v>100</v>
+      </c>
+      <c r="N35" s="1">
         <v>141242</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -2966,10 +3072,13 @@
         <v>100</v>
       </c>
       <c r="M36" s="1">
+        <v>100</v>
+      </c>
+      <c r="N36" s="1">
         <v>160262</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>1</v>
       </c>
@@ -3007,10 +3116,13 @@
         <v>100</v>
       </c>
       <c r="M37" s="1">
+        <v>100</v>
+      </c>
+      <c r="N37" s="1">
         <v>181139</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -3048,10 +3160,13 @@
         <v>100</v>
       </c>
       <c r="M38" s="1">
+        <v>100</v>
+      </c>
+      <c r="N38" s="1">
         <v>203985</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -3089,10 +3204,13 @@
         <v>100</v>
       </c>
       <c r="M39" s="1">
+        <v>100</v>
+      </c>
+      <c r="N39" s="1">
         <v>228917</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -3130,10 +3248,13 @@
         <v>100</v>
       </c>
       <c r="M40" s="1">
+        <v>100</v>
+      </c>
+      <c r="N40" s="1">
         <v>256053</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>1</v>
       </c>
@@ -3171,10 +3292,13 @@
         <v>100</v>
       </c>
       <c r="M41" s="1">
+        <v>100</v>
+      </c>
+      <c r="N41" s="1">
         <v>285510</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>1</v>
       </c>
@@ -3212,10 +3336,13 @@
         <v>100</v>
       </c>
       <c r="M42" s="1">
+        <v>100</v>
+      </c>
+      <c r="N42" s="1">
         <v>317411</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>1</v>
       </c>
@@ -3253,10 +3380,13 @@
         <v>100</v>
       </c>
       <c r="M43" s="1">
+        <v>100</v>
+      </c>
+      <c r="N43" s="1">
         <v>351878</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>1</v>
       </c>
@@ -3294,10 +3424,13 @@
         <v>100</v>
       </c>
       <c r="M44" s="1">
+        <v>100</v>
+      </c>
+      <c r="N44" s="1">
         <v>389035</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>1</v>
       </c>
@@ -3335,10 +3468,13 @@
         <v>100</v>
       </c>
       <c r="M45" s="1">
+        <v>100</v>
+      </c>
+      <c r="N45" s="1">
         <v>429007</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>1</v>
       </c>
@@ -3376,10 +3512,13 @@
         <v>100</v>
       </c>
       <c r="M46" s="1">
+        <v>100</v>
+      </c>
+      <c r="N46" s="1">
         <v>471919</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -3417,10 +3556,13 @@
         <v>100</v>
       </c>
       <c r="M47" s="1">
+        <v>100</v>
+      </c>
+      <c r="N47" s="1">
         <v>517898</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>1</v>
       </c>
@@ -3458,10 +3600,13 @@
         <v>100</v>
       </c>
       <c r="M48" s="1">
+        <v>100</v>
+      </c>
+      <c r="N48" s="1">
         <v>567071</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>1</v>
       </c>
@@ -3499,10 +3644,13 @@
         <v>100</v>
       </c>
       <c r="M49" s="1">
+        <v>100</v>
+      </c>
+      <c r="N49" s="1">
         <v>619565</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>1</v>
       </c>
@@ -3540,10 +3688,13 @@
         <v>100</v>
       </c>
       <c r="M50" s="1">
+        <v>100</v>
+      </c>
+      <c r="N50" s="1">
         <v>675508</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>1</v>
       </c>
@@ -3581,10 +3732,13 @@
         <v>100</v>
       </c>
       <c r="M51" s="1">
+        <v>100</v>
+      </c>
+      <c r="N51" s="1">
         <v>735027</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>1</v>
       </c>
@@ -3622,10 +3776,13 @@
         <v>100</v>
       </c>
       <c r="M52" s="1">
+        <v>100</v>
+      </c>
+      <c r="N52" s="1">
         <v>798251</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>1</v>
       </c>
@@ -3663,10 +3820,13 @@
         <v>100</v>
       </c>
       <c r="M53" s="1">
+        <v>100</v>
+      </c>
+      <c r="N53" s="1">
         <v>865305</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>1</v>
       </c>
@@ -3704,10 +3864,13 @@
         <v>100</v>
       </c>
       <c r="M54" s="1">
+        <v>100</v>
+      </c>
+      <c r="N54" s="1">
         <v>936085</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>1</v>
       </c>
@@ -3745,10 +3908,13 @@
         <v>100</v>
       </c>
       <c r="M55" s="1">
+        <v>100</v>
+      </c>
+      <c r="N55" s="1">
         <v>1006864</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>1</v>
       </c>
@@ -3786,10 +3952,13 @@
         <v>100</v>
       </c>
       <c r="M56" s="1">
+        <v>100</v>
+      </c>
+      <c r="N56" s="1">
         <v>1077644</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>1</v>
       </c>
@@ -3827,10 +3996,13 @@
         <v>100</v>
       </c>
       <c r="M57" s="1">
+        <v>100</v>
+      </c>
+      <c r="N57" s="1">
         <v>1148424</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>1</v>
       </c>
@@ -3868,10 +4040,13 @@
         <v>100</v>
       </c>
       <c r="M58" s="1">
+        <v>100</v>
+      </c>
+      <c r="N58" s="1">
         <v>1219204</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>1</v>
       </c>
@@ -3909,10 +4084,13 @@
         <v>100</v>
       </c>
       <c r="M59" s="1">
+        <v>100</v>
+      </c>
+      <c r="N59" s="1">
         <v>1289984</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>1</v>
       </c>
@@ -3950,10 +4128,13 @@
         <v>100</v>
       </c>
       <c r="M60" s="1">
+        <v>100</v>
+      </c>
+      <c r="N60" s="1">
         <v>1360763</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>1</v>
       </c>
@@ -3991,10 +4172,13 @@
         <v>100</v>
       </c>
       <c r="M61" s="1">
+        <v>100</v>
+      </c>
+      <c r="N61" s="1">
         <v>1431543</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>1</v>
       </c>
@@ -4032,10 +4216,13 @@
         <v>100</v>
       </c>
       <c r="M62" s="1">
+        <v>100</v>
+      </c>
+      <c r="N62" s="1">
         <v>1502323</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>1</v>
       </c>
@@ -4073,10 +4260,13 @@
         <v>100</v>
       </c>
       <c r="M63" s="1">
+        <v>100</v>
+      </c>
+      <c r="N63" s="1">
         <v>1573103</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>1</v>
       </c>
@@ -4114,10 +4304,13 @@
         <v>100</v>
       </c>
       <c r="M64" s="1">
+        <v>100</v>
+      </c>
+      <c r="N64" s="1">
         <v>1643883</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>1</v>
       </c>
@@ -4155,10 +4348,13 @@
         <v>100</v>
       </c>
       <c r="M65" s="1">
+        <v>100</v>
+      </c>
+      <c r="N65" s="1">
         <v>1714662</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>1</v>
       </c>
@@ -4196,10 +4392,13 @@
         <v>100</v>
       </c>
       <c r="M66" s="1">
+        <v>100</v>
+      </c>
+      <c r="N66" s="1">
         <v>1785442</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>1</v>
       </c>
@@ -4237,10 +4436,13 @@
         <v>100</v>
       </c>
       <c r="M67" s="1">
+        <v>100</v>
+      </c>
+      <c r="N67" s="1">
         <v>1856222</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>1</v>
       </c>
@@ -4278,10 +4480,13 @@
         <v>100</v>
       </c>
       <c r="M68" s="1">
+        <v>100</v>
+      </c>
+      <c r="N68" s="1">
         <v>1927002</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>1</v>
       </c>
@@ -4319,10 +4524,13 @@
         <v>100</v>
       </c>
       <c r="M69" s="1">
+        <v>100</v>
+      </c>
+      <c r="N69" s="1">
         <v>1997782</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>1</v>
       </c>
@@ -4360,10 +4568,13 @@
         <v>100</v>
       </c>
       <c r="M70" s="1">
+        <v>100</v>
+      </c>
+      <c r="N70" s="1">
         <v>2068561</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>1</v>
       </c>
@@ -4401,10 +4612,13 @@
         <v>100</v>
       </c>
       <c r="M71" s="1">
+        <v>100</v>
+      </c>
+      <c r="N71" s="1">
         <v>2139341</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>1</v>
       </c>
@@ -4442,10 +4656,13 @@
         <v>100</v>
       </c>
       <c r="M72" s="1">
+        <v>100</v>
+      </c>
+      <c r="N72" s="1">
         <v>2210121</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>1</v>
       </c>
@@ -4483,10 +4700,13 @@
         <v>100</v>
       </c>
       <c r="M73" s="1">
+        <v>100</v>
+      </c>
+      <c r="N73" s="1">
         <v>2280901</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>1</v>
       </c>
@@ -4524,10 +4744,13 @@
         <v>100</v>
       </c>
       <c r="M74" s="1">
+        <v>100</v>
+      </c>
+      <c r="N74" s="1">
         <v>2351681</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>1</v>
       </c>
@@ -4565,10 +4788,13 @@
         <v>100</v>
       </c>
       <c r="M75" s="1">
+        <v>100</v>
+      </c>
+      <c r="N75" s="1">
         <v>2422460</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>1</v>
       </c>
@@ -4606,10 +4832,13 @@
         <v>100</v>
       </c>
       <c r="M76" s="1">
+        <v>100</v>
+      </c>
+      <c r="N76" s="1">
         <v>2493240</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>1</v>
       </c>
@@ -4647,10 +4876,13 @@
         <v>100</v>
       </c>
       <c r="M77" s="1">
+        <v>100</v>
+      </c>
+      <c r="N77" s="1">
         <v>2564020</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>1</v>
       </c>
@@ -4688,10 +4920,13 @@
         <v>100</v>
       </c>
       <c r="M78" s="1">
+        <v>100</v>
+      </c>
+      <c r="N78" s="1">
         <v>2634800</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>1</v>
       </c>
@@ -4729,10 +4964,13 @@
         <v>100</v>
       </c>
       <c r="M79" s="1">
+        <v>100</v>
+      </c>
+      <c r="N79" s="1">
         <v>2705580</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>1</v>
       </c>
@@ -4770,10 +5008,13 @@
         <v>100</v>
       </c>
       <c r="M80" s="1">
+        <v>100</v>
+      </c>
+      <c r="N80" s="1">
         <v>2776359</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>1</v>
       </c>
@@ -4811,10 +5052,13 @@
         <v>100</v>
       </c>
       <c r="M81" s="1">
+        <v>100</v>
+      </c>
+      <c r="N81" s="1">
         <v>2847139</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>1</v>
       </c>
@@ -4852,10 +5096,13 @@
         <v>100</v>
       </c>
       <c r="M82" s="1">
+        <v>100</v>
+      </c>
+      <c r="N82" s="1">
         <v>2917919</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>1</v>
       </c>
@@ -4893,10 +5140,13 @@
         <v>100</v>
       </c>
       <c r="M83" s="1">
+        <v>100</v>
+      </c>
+      <c r="N83" s="1">
         <v>2988699</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>1</v>
       </c>
@@ -4934,10 +5184,13 @@
         <v>100</v>
       </c>
       <c r="M84" s="1">
+        <v>100</v>
+      </c>
+      <c r="N84" s="1">
         <v>3059479</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>1</v>
       </c>
@@ -4975,10 +5228,13 @@
         <v>100</v>
       </c>
       <c r="M85" s="1">
+        <v>100</v>
+      </c>
+      <c r="N85" s="1">
         <v>3130258</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>1</v>
       </c>
@@ -5016,10 +5272,13 @@
         <v>100</v>
       </c>
       <c r="M86" s="1">
+        <v>100</v>
+      </c>
+      <c r="N86" s="1">
         <v>3201038</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>1</v>
       </c>
@@ -5057,10 +5316,13 @@
         <v>100</v>
       </c>
       <c r="M87" s="1">
+        <v>100</v>
+      </c>
+      <c r="N87" s="1">
         <v>3271818</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>1</v>
       </c>
@@ -5098,10 +5360,13 @@
         <v>100</v>
       </c>
       <c r="M88" s="1">
+        <v>100</v>
+      </c>
+      <c r="N88" s="1">
         <v>3342598</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>1</v>
       </c>
@@ -5139,10 +5404,13 @@
         <v>100</v>
       </c>
       <c r="M89" s="1">
+        <v>100</v>
+      </c>
+      <c r="N89" s="1">
         <v>3413378</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>1</v>
       </c>
@@ -5180,10 +5448,13 @@
         <v>100</v>
       </c>
       <c r="M90" s="1">
+        <v>100</v>
+      </c>
+      <c r="N90" s="1">
         <v>3484157</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>1</v>
       </c>
@@ -5221,10 +5492,13 @@
         <v>100</v>
       </c>
       <c r="M91" s="1">
+        <v>100</v>
+      </c>
+      <c r="N91" s="1">
         <v>3554937</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>1</v>
       </c>
@@ -5262,10 +5536,13 @@
         <v>100</v>
       </c>
       <c r="M92" s="1">
+        <v>100</v>
+      </c>
+      <c r="N92" s="1">
         <v>3625717</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>1</v>
       </c>
@@ -5303,10 +5580,13 @@
         <v>100</v>
       </c>
       <c r="M93" s="1">
+        <v>100</v>
+      </c>
+      <c r="N93" s="1">
         <v>3696497</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>1</v>
       </c>
@@ -5344,10 +5624,13 @@
         <v>100</v>
       </c>
       <c r="M94" s="1">
+        <v>100</v>
+      </c>
+      <c r="N94" s="1">
         <v>3767277</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>1</v>
       </c>
@@ -5385,10 +5668,13 @@
         <v>100</v>
       </c>
       <c r="M95" s="1">
+        <v>100</v>
+      </c>
+      <c r="N95" s="1">
         <v>3838056</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>1</v>
       </c>
@@ -5426,10 +5712,13 @@
         <v>100</v>
       </c>
       <c r="M96" s="1">
+        <v>100</v>
+      </c>
+      <c r="N96" s="1">
         <v>3908836</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>1</v>
       </c>
@@ -5467,10 +5756,13 @@
         <v>100</v>
       </c>
       <c r="M97" s="1">
+        <v>100</v>
+      </c>
+      <c r="N97" s="1">
         <v>3979616</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>1</v>
       </c>
@@ -5508,10 +5800,13 @@
         <v>100</v>
       </c>
       <c r="M98" s="1">
+        <v>100</v>
+      </c>
+      <c r="N98" s="1">
         <v>4050396</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>1</v>
       </c>
@@ -5549,10 +5844,13 @@
         <v>100</v>
       </c>
       <c r="M99" s="1">
+        <v>100</v>
+      </c>
+      <c r="N99" s="1">
         <v>4121176</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>1</v>
       </c>
@@ -5590,10 +5888,13 @@
         <v>100</v>
       </c>
       <c r="M100" s="1">
+        <v>100</v>
+      </c>
+      <c r="N100" s="1">
         <v>4191955</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>1</v>
       </c>
@@ -5631,10 +5932,13 @@
         <v>100</v>
       </c>
       <c r="M101" s="1">
+        <v>100</v>
+      </c>
+      <c r="N101" s="1">
         <v>4262735</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>1</v>
       </c>
@@ -5672,10 +5976,13 @@
         <v>100</v>
       </c>
       <c r="M102" s="1">
+        <v>100</v>
+      </c>
+      <c r="N102" s="1">
         <v>4333515</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>1</v>
       </c>
@@ -5713,6 +6020,9 @@
         <v>100</v>
       </c>
       <c r="M103" s="1">
+        <v>100</v>
+      </c>
+      <c r="N103" s="1">
         <v>4404295</v>
       </c>
     </row>

--- a/Datas/ProfessionDataList.xlsx
+++ b/Datas/ProfessionDataList.xlsx
@@ -1667,7 +1667,7 @@
         <v>100</v>
       </c>
       <c r="N4" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.15">
@@ -1711,7 +1711,7 @@
         <v>100</v>
       </c>
       <c r="N5" s="1">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.15">
@@ -1755,7 +1755,7 @@
         <v>100</v>
       </c>
       <c r="N6" s="1">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.15">
@@ -1799,7 +1799,7 @@
         <v>100</v>
       </c>
       <c r="N7" s="1">
-        <v>62</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.15">
@@ -1843,7 +1843,7 @@
         <v>100</v>
       </c>
       <c r="N8" s="1">
-        <v>109</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.15">
@@ -1887,7 +1887,7 @@
         <v>100</v>
       </c>
       <c r="N9" s="1">
-        <v>186</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.15">
@@ -1931,7 +1931,7 @@
         <v>100</v>
       </c>
       <c r="N10" s="1">
-        <v>311</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.15">
@@ -1975,7 +1975,7 @@
         <v>100</v>
       </c>
       <c r="N11" s="1">
-        <v>503</v>
+        <v>786</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.15">
@@ -2019,7 +2019,7 @@
         <v>100</v>
       </c>
       <c r="N12" s="1">
-        <v>786</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.15">
@@ -2063,7 +2063,7 @@
         <v>100</v>
       </c>
       <c r="N13" s="1">
-        <v>1187</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.15">
@@ -2107,7 +2107,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="1">
-        <v>1738</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.15">
@@ -2151,7 +2151,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="1">
-        <v>2472</v>
+        <v>3428</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.15">
@@ -2195,7 +2195,7 @@
         <v>100</v>
       </c>
       <c r="N16" s="1">
-        <v>3428</v>
+        <v>4649</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.15">
@@ -2239,7 +2239,7 @@
         <v>100</v>
       </c>
       <c r="N17" s="1">
-        <v>4649</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.15">
@@ -2283,7 +2283,7 @@
         <v>100</v>
       </c>
       <c r="N18" s="1">
-        <v>6178</v>
+        <v>8067</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.15">
@@ -2327,7 +2327,7 @@
         <v>100</v>
       </c>
       <c r="N19" s="1">
-        <v>8067</v>
+        <v>10366</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.15">
@@ -2371,7 +2371,7 @@
         <v>100</v>
       </c>
       <c r="N20" s="1">
-        <v>10366</v>
+        <v>13134</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.15">
@@ -2415,7 +2415,7 @@
         <v>100</v>
       </c>
       <c r="N21" s="1">
-        <v>13134</v>
+        <v>16429</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.15">
@@ -2459,7 +2459,7 @@
         <v>100</v>
       </c>
       <c r="N22" s="1">
-        <v>16429</v>
+        <v>20315</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.15">
@@ -2503,7 +2503,7 @@
         <v>100</v>
       </c>
       <c r="N23" s="1">
-        <v>20315</v>
+        <v>24861</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.15">
@@ -2547,7 +2547,7 @@
         <v>100</v>
       </c>
       <c r="N24" s="1">
-        <v>24861</v>
+        <v>30136</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.15">
@@ -2591,7 +2591,7 @@
         <v>100</v>
       </c>
       <c r="N25" s="1">
-        <v>30136</v>
+        <v>36216</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.15">
@@ -2635,7 +2635,7 @@
         <v>100</v>
       </c>
       <c r="N26" s="1">
-        <v>36216</v>
+        <v>43178</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.15">
@@ -2679,7 +2679,7 @@
         <v>100</v>
       </c>
       <c r="N27" s="1">
-        <v>43178</v>
+        <v>51105</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.15">
@@ -2723,7 +2723,7 @@
         <v>100</v>
       </c>
       <c r="N28" s="1">
-        <v>51105</v>
+        <v>60082</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.15">
@@ -2767,7 +2767,7 @@
         <v>100</v>
       </c>
       <c r="N29" s="1">
-        <v>60082</v>
+        <v>70199</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.15">
@@ -2811,7 +2811,7 @@
         <v>100</v>
       </c>
       <c r="N30" s="1">
-        <v>70199</v>
+        <v>81547</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.15">
@@ -2855,7 +2855,7 @@
         <v>100</v>
       </c>
       <c r="N31" s="1">
-        <v>81547</v>
+        <v>94225</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.15">
@@ -2899,7 +2899,7 @@
         <v>100</v>
       </c>
       <c r="N32" s="1">
-        <v>94225</v>
+        <v>108330</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.15">
@@ -2943,7 +2943,7 @@
         <v>100</v>
       </c>
       <c r="N33" s="1">
-        <v>108330</v>
+        <v>123968</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.15">
@@ -2987,7 +2987,7 @@
         <v>100</v>
       </c>
       <c r="N34" s="1">
-        <v>123968</v>
+        <v>141242</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.15">
@@ -3031,7 +3031,7 @@
         <v>100</v>
       </c>
       <c r="N35" s="1">
-        <v>141242</v>
+        <v>160262</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.15">
@@ -3075,7 +3075,7 @@
         <v>100</v>
       </c>
       <c r="N36" s="1">
-        <v>160262</v>
+        <v>181139</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.15">
@@ -3119,7 +3119,7 @@
         <v>100</v>
       </c>
       <c r="N37" s="1">
-        <v>181139</v>
+        <v>203985</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.15">
@@ -3163,7 +3163,7 @@
         <v>100</v>
       </c>
       <c r="N38" s="1">
-        <v>203985</v>
+        <v>228917</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.15">
@@ -3207,7 +3207,7 @@
         <v>100</v>
       </c>
       <c r="N39" s="1">
-        <v>228917</v>
+        <v>256053</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.15">
@@ -3251,7 +3251,7 @@
         <v>100</v>
       </c>
       <c r="N40" s="1">
-        <v>256053</v>
+        <v>285510</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.15">
@@ -3295,7 +3295,7 @@
         <v>100</v>
       </c>
       <c r="N41" s="1">
-        <v>285510</v>
+        <v>317411</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.15">
@@ -3339,7 +3339,7 @@
         <v>100</v>
       </c>
       <c r="N42" s="1">
-        <v>317411</v>
+        <v>351878</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.15">
@@ -3383,7 +3383,7 @@
         <v>100</v>
       </c>
       <c r="N43" s="1">
-        <v>351878</v>
+        <v>389035</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.15">
@@ -3427,7 +3427,7 @@
         <v>100</v>
       </c>
       <c r="N44" s="1">
-        <v>389035</v>
+        <v>429007</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.15">
@@ -3471,7 +3471,7 @@
         <v>100</v>
       </c>
       <c r="N45" s="1">
-        <v>429007</v>
+        <v>471919</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.15">
@@ -3515,7 +3515,7 @@
         <v>100</v>
       </c>
       <c r="N46" s="1">
-        <v>471919</v>
+        <v>517898</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.15">
@@ -3559,7 +3559,7 @@
         <v>100</v>
       </c>
       <c r="N47" s="1">
-        <v>517898</v>
+        <v>567071</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.15">
@@ -3603,7 +3603,7 @@
         <v>100</v>
       </c>
       <c r="N48" s="1">
-        <v>567071</v>
+        <v>619565</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.15">
@@ -3647,7 +3647,7 @@
         <v>100</v>
       </c>
       <c r="N49" s="1">
-        <v>619565</v>
+        <v>675508</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.15">
@@ -3691,7 +3691,7 @@
         <v>100</v>
       </c>
       <c r="N50" s="1">
-        <v>675508</v>
+        <v>735027</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.15">
@@ -3735,7 +3735,7 @@
         <v>100</v>
       </c>
       <c r="N51" s="1">
-        <v>735027</v>
+        <v>798251</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.15">
@@ -3779,7 +3779,7 @@
         <v>100</v>
       </c>
       <c r="N52" s="1">
-        <v>798251</v>
+        <v>865305</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.15">
@@ -3823,7 +3823,7 @@
         <v>100</v>
       </c>
       <c r="N53" s="1">
-        <v>865305</v>
+        <v>936085</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.15">
@@ -3867,7 +3867,7 @@
         <v>100</v>
       </c>
       <c r="N54" s="1">
-        <v>936085</v>
+        <v>1006864</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.15">
@@ -3911,7 +3911,7 @@
         <v>100</v>
       </c>
       <c r="N55" s="1">
-        <v>1006864</v>
+        <v>1077644</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.15">
@@ -3955,7 +3955,7 @@
         <v>100</v>
       </c>
       <c r="N56" s="1">
-        <v>1077644</v>
+        <v>1148424</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.15">
@@ -3999,7 +3999,7 @@
         <v>100</v>
       </c>
       <c r="N57" s="1">
-        <v>1148424</v>
+        <v>1219204</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.15">
@@ -4043,7 +4043,7 @@
         <v>100</v>
       </c>
       <c r="N58" s="1">
-        <v>1219204</v>
+        <v>1289984</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.15">
@@ -4087,7 +4087,7 @@
         <v>100</v>
       </c>
       <c r="N59" s="1">
-        <v>1289984</v>
+        <v>1360763</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.15">
@@ -4131,7 +4131,7 @@
         <v>100</v>
       </c>
       <c r="N60" s="1">
-        <v>1360763</v>
+        <v>1431543</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.15">
@@ -4175,7 +4175,7 @@
         <v>100</v>
       </c>
       <c r="N61" s="1">
-        <v>1431543</v>
+        <v>1502323</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.15">
@@ -4219,7 +4219,7 @@
         <v>100</v>
       </c>
       <c r="N62" s="1">
-        <v>1502323</v>
+        <v>1573103</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.15">
@@ -4263,7 +4263,7 @@
         <v>100</v>
       </c>
       <c r="N63" s="1">
-        <v>1573103</v>
+        <v>1643883</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.15">
@@ -4307,7 +4307,7 @@
         <v>100</v>
       </c>
       <c r="N64" s="1">
-        <v>1643883</v>
+        <v>1714662</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.15">
@@ -4351,7 +4351,7 @@
         <v>100</v>
       </c>
       <c r="N65" s="1">
-        <v>1714662</v>
+        <v>1785442</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.15">
@@ -4395,7 +4395,7 @@
         <v>100</v>
       </c>
       <c r="N66" s="1">
-        <v>1785442</v>
+        <v>1856222</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.15">
@@ -4439,7 +4439,7 @@
         <v>100</v>
       </c>
       <c r="N67" s="1">
-        <v>1856222</v>
+        <v>1927002</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.15">
@@ -4483,7 +4483,7 @@
         <v>100</v>
       </c>
       <c r="N68" s="1">
-        <v>1927002</v>
+        <v>1997782</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.15">
@@ -4527,7 +4527,7 @@
         <v>100</v>
       </c>
       <c r="N69" s="1">
-        <v>1997782</v>
+        <v>2068561</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.15">
@@ -4571,7 +4571,7 @@
         <v>100</v>
       </c>
       <c r="N70" s="1">
-        <v>2068561</v>
+        <v>2139341</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.15">
@@ -4615,7 +4615,7 @@
         <v>100</v>
       </c>
       <c r="N71" s="1">
-        <v>2139341</v>
+        <v>2210121</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.15">
@@ -4659,7 +4659,7 @@
         <v>100</v>
       </c>
       <c r="N72" s="1">
-        <v>2210121</v>
+        <v>2280901</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.15">
@@ -4703,7 +4703,7 @@
         <v>100</v>
       </c>
       <c r="N73" s="1">
-        <v>2280901</v>
+        <v>2351681</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.15">
@@ -4747,7 +4747,7 @@
         <v>100</v>
       </c>
       <c r="N74" s="1">
-        <v>2351681</v>
+        <v>2422460</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.15">
@@ -4791,7 +4791,7 @@
         <v>100</v>
       </c>
       <c r="N75" s="1">
-        <v>2422460</v>
+        <v>2493240</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.15">
@@ -4835,7 +4835,7 @@
         <v>100</v>
       </c>
       <c r="N76" s="1">
-        <v>2493240</v>
+        <v>2564020</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.15">
@@ -4879,7 +4879,7 @@
         <v>100</v>
       </c>
       <c r="N77" s="1">
-        <v>2564020</v>
+        <v>2634800</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.15">
@@ -4923,7 +4923,7 @@
         <v>100</v>
       </c>
       <c r="N78" s="1">
-        <v>2634800</v>
+        <v>2705580</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.15">
@@ -4967,7 +4967,7 @@
         <v>100</v>
       </c>
       <c r="N79" s="1">
-        <v>2705580</v>
+        <v>2776359</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.15">
@@ -5011,7 +5011,7 @@
         <v>100</v>
       </c>
       <c r="N80" s="1">
-        <v>2776359</v>
+        <v>2847139</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.15">
@@ -5055,7 +5055,7 @@
         <v>100</v>
       </c>
       <c r="N81" s="1">
-        <v>2847139</v>
+        <v>2917919</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.15">
@@ -5099,7 +5099,7 @@
         <v>100</v>
       </c>
       <c r="N82" s="1">
-        <v>2917919</v>
+        <v>2988699</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.15">
@@ -5143,7 +5143,7 @@
         <v>100</v>
       </c>
       <c r="N83" s="1">
-        <v>2988699</v>
+        <v>3059479</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.15">
@@ -5187,7 +5187,7 @@
         <v>100</v>
       </c>
       <c r="N84" s="1">
-        <v>3059479</v>
+        <v>3130258</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.15">
@@ -5231,7 +5231,7 @@
         <v>100</v>
       </c>
       <c r="N85" s="1">
-        <v>3130258</v>
+        <v>3201038</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.15">
@@ -5275,7 +5275,7 @@
         <v>100</v>
       </c>
       <c r="N86" s="1">
-        <v>3201038</v>
+        <v>3271818</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.15">
@@ -5319,7 +5319,7 @@
         <v>100</v>
       </c>
       <c r="N87" s="1">
-        <v>3271818</v>
+        <v>3342598</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.15">
@@ -5363,7 +5363,7 @@
         <v>100</v>
       </c>
       <c r="N88" s="1">
-        <v>3342598</v>
+        <v>3413378</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.15">
@@ -5407,7 +5407,7 @@
         <v>100</v>
       </c>
       <c r="N89" s="1">
-        <v>3413378</v>
+        <v>3484157</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.15">
@@ -5451,7 +5451,7 @@
         <v>100</v>
       </c>
       <c r="N90" s="1">
-        <v>3484157</v>
+        <v>3554937</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.15">
@@ -5495,7 +5495,7 @@
         <v>100</v>
       </c>
       <c r="N91" s="1">
-        <v>3554937</v>
+        <v>3625717</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.15">
@@ -5539,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="N92" s="1">
-        <v>3625717</v>
+        <v>3696497</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.15">
@@ -5583,7 +5583,7 @@
         <v>100</v>
       </c>
       <c r="N93" s="1">
-        <v>3696497</v>
+        <v>3767277</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.15">
@@ -5627,7 +5627,7 @@
         <v>100</v>
       </c>
       <c r="N94" s="1">
-        <v>3767277</v>
+        <v>3838056</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.15">
@@ -5671,7 +5671,7 @@
         <v>100</v>
       </c>
       <c r="N95" s="1">
-        <v>3838056</v>
+        <v>3908836</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.15">
@@ -5715,7 +5715,7 @@
         <v>100</v>
       </c>
       <c r="N96" s="1">
-        <v>3908836</v>
+        <v>3979616</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.15">
@@ -5759,7 +5759,7 @@
         <v>100</v>
       </c>
       <c r="N97" s="1">
-        <v>3979616</v>
+        <v>4050396</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.15">
@@ -5803,7 +5803,7 @@
         <v>100</v>
       </c>
       <c r="N98" s="1">
-        <v>4050396</v>
+        <v>4121176</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.15">
@@ -5847,7 +5847,7 @@
         <v>100</v>
       </c>
       <c r="N99" s="1">
-        <v>4121176</v>
+        <v>4191955</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.15">
@@ -5891,7 +5891,7 @@
         <v>100</v>
       </c>
       <c r="N100" s="1">
-        <v>4191955</v>
+        <v>4262735</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.15">
@@ -5935,7 +5935,7 @@
         <v>100</v>
       </c>
       <c r="N101" s="1">
-        <v>4262735</v>
+        <v>4333515</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.15">
@@ -5979,7 +5979,7 @@
         <v>100</v>
       </c>
       <c r="N102" s="1">
-        <v>4333515</v>
+        <v>4404295</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.15">
@@ -6023,7 +6023,7 @@
         <v>100</v>
       </c>
       <c r="N103" s="1">
-        <v>4404295</v>
+        <v>4475075</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ProfessionDataList.xlsx
+++ b/Datas/ProfessionDataList.xlsx
@@ -5,15 +5,16 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory_hub\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380"/>
+    <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ProfessionData" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ProfessionData!$A$3:$A$3</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="364">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1145,6 +1146,69 @@
   <si>
     <t>Speed</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长剑</t>
+  </si>
+  <si>
+    <t>诅咒之剑</t>
+  </si>
+  <si>
+    <t>烈焰之刃</t>
+  </si>
+  <si>
+    <t>大地之剑</t>
+  </si>
+  <si>
+    <t>冰之刃</t>
+  </si>
+  <si>
+    <t>铁枪</t>
+  </si>
+  <si>
+    <t>骑士长枪</t>
+  </si>
+  <si>
+    <t>血腥之枪</t>
+  </si>
+  <si>
+    <t>三叉戟</t>
+  </si>
+  <si>
+    <t>战斧</t>
+  </si>
+  <si>
+    <t>毒蜥之牙</t>
+  </si>
+  <si>
+    <t>恶魔之斧</t>
+  </si>
+  <si>
+    <t>蛇皮鞭</t>
+  </si>
+  <si>
+    <t>藤鞭</t>
+  </si>
+  <si>
+    <t>女王鞭</t>
+  </si>
+  <si>
+    <t>蛇牙鞭</t>
+  </si>
+  <si>
+    <t>暴雪斧</t>
+  </si>
+  <si>
+    <t>秘银长剑</t>
+  </si>
+  <si>
+    <t>幻影长枪</t>
+  </si>
+  <si>
+    <t>雷神之鞭</t>
+  </si>
+  <si>
+    <t>死亡之鞭</t>
   </si>
 </sst>
 </file>
@@ -6040,6 +6104,239 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C3:H23"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F4" t="s">
+        <v>348</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C5" t="s">
+        <v>346</v>
+      </c>
+      <c r="F5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C6" t="s">
+        <v>347</v>
+      </c>
+      <c r="F6" t="s">
+        <v>355</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="F7" t="s">
+        <v>352</v>
+      </c>
+      <c r="H7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F8" t="s">
+        <v>344</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F9" t="s">
+        <v>349</v>
+      </c>
+      <c r="H9">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C10" t="s">
+        <v>351</v>
+      </c>
+      <c r="F10" t="s">
+        <v>353</v>
+      </c>
+      <c r="H10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C11" t="s">
+        <v>352</v>
+      </c>
+      <c r="F11" t="s">
+        <v>350</v>
+      </c>
+      <c r="H11">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C12" t="s">
+        <v>353</v>
+      </c>
+      <c r="F12" t="s">
+        <v>357</v>
+      </c>
+      <c r="H12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C13" t="s">
+        <v>354</v>
+      </c>
+      <c r="F13" t="s">
+        <v>346</v>
+      </c>
+      <c r="H13">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C14" t="s">
+        <v>355</v>
+      </c>
+      <c r="F14" t="s">
+        <v>358</v>
+      </c>
+      <c r="H14">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="F15" t="s">
+        <v>351</v>
+      </c>
+      <c r="H15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C16" t="s">
+        <v>357</v>
+      </c>
+      <c r="F16" t="s">
+        <v>354</v>
+      </c>
+      <c r="H16">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C17" t="s">
+        <v>358</v>
+      </c>
+      <c r="F17" t="s">
+        <v>345</v>
+      </c>
+      <c r="H17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C18" t="s">
+        <v>359</v>
+      </c>
+      <c r="F18" t="s">
+        <v>347</v>
+      </c>
+      <c r="H18">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C19" t="s">
+        <v>360</v>
+      </c>
+      <c r="F19" t="s">
+        <v>360</v>
+      </c>
+      <c r="H19">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C20" t="s">
+        <v>361</v>
+      </c>
+      <c r="F20" t="s">
+        <v>362</v>
+      </c>
+      <c r="H20">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C21" t="s">
+        <v>362</v>
+      </c>
+      <c r="F21" t="s">
+        <v>359</v>
+      </c>
+      <c r="H21">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="C22" t="s">
+        <v>363</v>
+      </c>
+      <c r="F22" t="s">
+        <v>361</v>
+      </c>
+      <c r="H22">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.15">
+      <c r="F23" t="s">
+        <v>363</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:I300"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>

--- a/Datas/ProfessionDataList.xlsx
+++ b/Datas/ProfessionDataList.xlsx
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="G4">
         <v>26</v>
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="1">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="G104">
         <v>20</v>
@@ -10523,7 +10523,7 @@
         <v>0</v>
       </c>
       <c r="F204" s="1">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="G204">
         <v>26</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="F304" s="1">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="G304">
         <v>26</v>
@@ -19323,7 +19323,7 @@
         <v>0</v>
       </c>
       <c r="F404" s="1">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="G404">
         <v>39</v>
